--- a/data/ams_weekly_data/Nexlev/ads_report_week13.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week13.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/data/ams_weekly_data/Nexlev/ads_report_week13.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week13.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
